--- a/management_forms/046_warehouse_staff_id_reissue_request_form--management_forms.xlsx
+++ b/management_forms/046_warehouse_staff_id_reissue_request_form--management_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -889,8 +889,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -918,12 +918,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'email',_'label':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'email', 'label': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -935,12 +935,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'phone',_'label':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'phone', 'label': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -952,12 +952,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'warehouse_operations',_'label':_'warehouse_operations'}</t>
+          <t>warehouse_operations</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Warehouse Operations', 'label': 'Warehouse Operations'}</t>
+          <t>Warehouse Operations</t>
         </is>
       </c>
     </row>
@@ -969,12 +969,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'hr',_'label':_'hr'}</t>
+          <t>hr</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'HR', 'label': 'HR'}</t>
+          <t>HR</t>
         </is>
       </c>
     </row>
@@ -986,12 +986,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'operations_management',_'label':_'operations_management'}</t>
+          <t>operations_management</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Operations Management', 'label': 'Operations Management'}</t>
+          <t>Operations Management</t>
         </is>
       </c>
     </row>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'warehouse_staff',_'label':_'warehouse_staff'}</t>
+          <t>warehouse_staff</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Warehouse Staff', 'label': 'Warehouse Staff'}</t>
+          <t>Warehouse Staff</t>
         </is>
       </c>
     </row>
@@ -1020,12 +1020,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'operations',_'label':_'operations'}</t>
+          <t>operations</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Operations', 'label': 'Operations'}</t>
+          <t>Operations</t>
         </is>
       </c>
     </row>
@@ -1037,12 +1037,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'hr',_'label':_'hr'}</t>
+          <t>hr</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'HR', 'label': 'HR'}</t>
+          <t>HR</t>
         </is>
       </c>
     </row>
@@ -1054,12 +1054,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'pending',_'label':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'pending', 'label': 'Pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'approved',_'label':_'approved'}</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'approved', 'label': 'Approved'}</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -1088,12 +1088,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'denied',_'label':_'denied'}</t>
+          <t>denied</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'denied', 'label': 'Denied'}</t>
+          <t>Denied</t>
         </is>
       </c>
     </row>
